--- a/wuying-gpu-customers.xlsx
+++ b/wuying-gpu-customers.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与来源" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户工商信息表'!$A$2:$K$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户工商信息表'!$A$2:$K$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1058,19 +1058,19 @@
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>⚪ 公海</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>🔵 关联可争取</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>光轮智能</t>
+          <t>原力灵机</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>光轮智能(北京)科技股份有限公司</t>
+          <t>北京原力灵机智能科技有限公司</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>北京市海淀区小月河东畔路16号院2号楼6层101</t>
+          <t>北京市海淀区西三旗建材城内1幢3层317号</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1090,44 +1090,44 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>杨海波</t>
+          <t>唐文斌</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>91110114MAC73BHP4P</t>
+          <t>91110108MAEE20TQ3A</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>289.10万元</t>
+          <t>1000万元</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Guanglun Intelligent (Beijing) Technology Co., Ltd.；具身仿真「卖水人」</t>
+          <t>Dexmal；具身原生大模型DM0(2.4B)及Dexbotic开发框架/DFOL量产工作流；旷视系(唐文斌创立)；A+轮由阿里巴巴领投</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>⚪ 公海</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>🔵 关联可争取</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>德塔智能</t>
+          <t>生数科技</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>北京德塔源创智能科技有限公司</t>
+          <t>北京生数科技股份有限公司</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1137,37 +1137,37 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>北京市（人形机器人基础模型）</t>
+          <t>北京市海淀区中关村东路8号东升大厦AB座八层801A单元</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>科技推广和应用服务业</t>
+          <t>软件和信息技术服务业</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>马晓健（创始人）</t>
+          <t>鲍凡</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91110108MACC4D63XF</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>近5亿元天使++轮</t>
+          <t>1701.0235万元</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>人形机器人基础模型，成立即获大额融资</t>
+          <t>Shengshu/Vidu；联合清华发布视频大模型Vidu；A++轮由阿里云领投；具身世界模型方向</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>银河通用</t>
+          <t>光轮智能</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>北京银河通用机器人股份有限公司</t>
+          <t>光轮智能(北京)科技股份有限公司</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1194,37 +1194,37 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>北京市海淀区海淀大街3号1幢14层1401</t>
+          <t>北京市海淀区小月河东畔路16号院2号楼6层101</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>通用设备制造业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>姚腾洲</t>
+          <t>杨海波</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>91110108MACJ3J0D0R</t>
+          <t>91110114MAC73BHP4P</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1756.34万元</t>
+          <t>289.10万元</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Beijing Galaxy General Robotics Co., Ltd.</t>
+          <t>Guanglun Intelligent (Beijing) Technology Co., Ltd.；具身仿真「卖水人」</t>
         </is>
       </c>
     </row>
@@ -1236,52 +1236,52 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>千寻智能</t>
+          <t>德塔智能</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>千寻智能(杭州)科技有限公司</t>
+          <t>北京德塔源创智能科技有限公司</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区宁围街道利一路188号天人大厦浙大研究院数字经济孵化器4层401室-38</t>
+          <t>北京市（人形机器人基础模型）</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>软件和信息技术服务业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>韩峰涛</t>
+          <t>马晓健（创始人）</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>91330109MAD9M4GQ4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>近5亿元天使++轮</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>具身智能本体研发</t>
+          <t>人形机器人基础模型，成立即获大额融资</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>跨维智能</t>
+          <t>银河通用</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>跨维(深圳)智能数字科技有限公司</t>
+          <t>北京银河通用机器人股份有限公司</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>广东省深圳市南山区科园路1001号创投大厦14层</t>
+          <t>北京市海淀区海淀大街3号1幢14层1401</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -1318,27 +1318,27 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>贾俊</t>
+          <t>姚腾洲</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>91440300MA5GU4PM4C</t>
+          <t>91110108MACJ3J0D0R</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>223.46万元</t>
+          <t>1756.34万元</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>DexForce Technology Co., Ltd.；3D视觉具身</t>
+          <t>Beijing Galaxy General Robotics Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>云深处</t>
+          <t>千寻智能</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>云深处科技股份有限公司（更名自杭州云深处科技有限公司）</t>
+          <t>千寻智能(杭州)科技有限公司</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1365,27 +1365,27 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>浙江省杭州市西湖区三墩镇振华路666号名栖首座3号楼3层318-2室</t>
+          <t>浙江省杭州市萧山区宁围街道利一路188号天人大厦浙大研究院数字经济孵化器4层401室-38</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>通用设备制造业</t>
+          <t>软件和信息技术服务业</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>朱秋国</t>
+          <t>韩峰涛</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>91330106MA2AYE3K6X</t>
+          <t>91330109MAD9M4GQ4M</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Hangzhou Yunshenchu Technology Co.,Ltd.；四足机器人</t>
+          <t>具身智能本体研发</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>众擎机器人</t>
+          <t>跨维智能</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>深圳众擎机器人科技股份有限公司</t>
+          <t>跨维(深圳)智能数字科技有限公司</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1422,37 +1422,37 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>深圳市南山区粤海街道高新区社区科苑南路3156号深圳湾创新科技中心2栋A座2603</t>
+          <t>广东省深圳市南山区科园路1001号创投大厦14层</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>软件和信息技术服务业</t>
+          <t>通用设备制造业</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>赵同阳</t>
+          <t>贾俊</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>91440300MAD0L2XT8K</t>
+          <t>91440300MA5GU4PM4C</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>3206.75万元</t>
+          <t>223.46万元</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>EngineAI；人形机器人本体</t>
+          <t>DexForce Technology Co., Ltd.；3D视觉具身</t>
         </is>
       </c>
     </row>
@@ -1464,42 +1464,42 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>逐际动力</t>
+          <t>云深处</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>深圳逐际动力科技股份有限公司</t>
+          <t>云深处科技股份有限公司（更名自杭州云深处科技有限公司）</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>深圳市前海深港合作区南山街道兴海大道3046号香江金融大厦1511-009A</t>
+          <t>浙江省杭州市西湖区三墩镇振华路666号名栖首座3号楼3层318-2室</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>批发业</t>
+          <t>通用设备制造业</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>庞博</t>
+          <t>朱秋国</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>91440300MA5H6B6A43</t>
+          <t>91330106MA2AYE3K6X</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2017-11-29</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>LimX Dynamics；足式机器人</t>
+          <t>Hangzhou Yunshenchu Technology Co.,Ltd.；四足机器人</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>乐聚机器人</t>
+          <t>众擎机器人</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>乐聚智能(深圳)股份有限公司（更名自乐聚(深圳)机器人技术有限公司）</t>
+          <t>深圳众擎机器人科技股份有限公司</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1536,37 +1536,37 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>深圳市龙华区观湖街道樟溪社区观澜平安路22号4栋601</t>
+          <t>深圳市南山区粤海街道高新区社区科苑南路3156号深圳湾创新科技中心2栋A座2603</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>计算机/通信/电子设备制造业</t>
+          <t>软件和信息技术服务业</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>冷晓琨</t>
+          <t>赵同阳</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>91440300MA5D95FC4R</t>
+          <t>91440300MAD0L2XT8K</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>2016-03-24</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>6000万元</t>
+          <t>3206.75万元</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>LEJU(SHENZHEN) ROBOTICS CO.LTD；人形机器人</t>
+          <t>EngineAI；人形机器人本体</t>
         </is>
       </c>
     </row>
@@ -1578,52 +1578,52 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>星动纪元</t>
+          <t>逐际动力</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>北京星动纪元科技股份有限公司</t>
+          <t>深圳逐际动力科技股份有限公司</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>北京市海淀区中关村东路1号院7号楼7层701</t>
+          <t>深圳市前海深港合作区南山街道兴海大道3046号香江金融大厦1511-009A</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>通用设备制造业</t>
+          <t>批发业</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>张志</t>
+          <t>庞博</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>91110108MACTH7TU73</t>
+          <t>91440300MA5H6B6A43</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2094.2546万元</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Beijing Xingdong Era Technology Co., Ltd.；清华交叉信息研究院孵化，陈建宇教授领衔；顺丰领投超2亿美元</t>
+          <t>LimX Dynamics；足式机器人</t>
         </is>
       </c>
     </row>
@@ -1635,52 +1635,52 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>傅利叶智能</t>
+          <t>乐聚机器人</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上海傅利叶智能科技股份有限公司</t>
+          <t>乐聚智能(深圳)股份有限公司（更名自乐聚(深圳)机器人技术有限公司）</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>上海市浦东新区秀浦路2388号12幢1层101室、2层</t>
+          <t>深圳市龙华区观湖街道樟溪社区观澜平安路22号4栋601</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>通用设备制造业</t>
+          <t>计算机/通信/电子设备制造业</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>顾捷</t>
+          <t>冷晓琨</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>9131000035105342XD</t>
+          <t>91440300MA5D95FC4R</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>2015-07-30</t>
+          <t>2016-03-24</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>404.9362万元</t>
+          <t>6000万元</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Fourier Intelligence Co., Ltd.；康复机器人+通用人形GR系列，具身智能老牌厂商</t>
+          <t>LEJU(SHENZHEN) ROBOTICS CO.LTD；人形机器人</t>
         </is>
       </c>
     </row>
@@ -1692,52 +1692,52 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>开普勒</t>
+          <t>星动纪元</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上海开普勒机器人有限公司</t>
+          <t>北京星动纪元科技股份有限公司</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>中国(上海)自贸试验区上科路366号、川和路55弄12号楼1层</t>
+          <t>北京市海淀区中关村东路1号院7号楼7层701</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>软件和信息服务业</t>
+          <t>通用设备制造业</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>杨华</t>
+          <t>张志</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>91310115MACUM2Q15M</t>
+          <t>91110108MACTH7TU73</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>410.5661万元</t>
+          <t>2094.2546万元</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Kepler Robot Co., Ltd.；曾用名 上海开普勒探索机器人有限公司；通用人形机器人</t>
+          <t>Beijing Xingdong Era Technology Co., Ltd.；清华交叉信息研究院孵化，陈建宇教授领衔；顺丰领投超2亿美元</t>
         </is>
       </c>
     </row>
@@ -1749,52 +1749,52 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>智平方</t>
+          <t>傅利叶智能</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>智平方(深圳)科技股份有限公司</t>
+          <t>上海傅利叶智能科技股份有限公司</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>深圳市南山区桃源街道福光社区留仙大道3370号南山智园崇文园区1号楼1904</t>
+          <t>上海市浦东新区秀浦路2388号12幢1层101室、2层</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>科技推广和应用服务业</t>
+          <t>通用设备制造业</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>郭彦东</t>
+          <t>顾捷</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>91440300MA5HTHDC7C</t>
+          <t>9131000035105342XD</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2015-07-30</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>249.3648万元</t>
+          <t>404.9362万元</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Zhifang (Shenzhen) Technology Co., Ltd.；郭彦东博士(前OPPO/小鹏AI首席科学家)创建；AlphaBot通用机器人；估值约200亿</t>
+          <t>Shanghai Fourier Intelligence Co., Ltd.；康复机器人+通用人形GR系列，具身智能老牌厂商</t>
         </is>
       </c>
     </row>
@@ -1806,52 +1806,52 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>松延动力</t>
+          <t>开普勒</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>北京松延动力科技集团股份有限公司</t>
+          <t>上海开普勒机器人有限公司</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>北京市昌平区未来科技城滨河大道3号院1号楼1601-1606房间</t>
+          <t>中国(上海)自贸试验区上科路366号、川和路55弄12号楼1层</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>科技推广和应用服务业</t>
+          <t>软件和信息服务业</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>姜哲源</t>
+          <t>杨华</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>91110114MACYMUGC1P</t>
+          <t>91310115MACUM2Q15M</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>459.6054万元</t>
+          <t>410.5661万元</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Songyan Power (Beijing) Technology Co., Ltd.；清华交叉信息学院背景；N2/S1人形机器人</t>
+          <t>Shanghai Kepler Robot Co., Ltd.；曾用名 上海开普勒探索机器人有限公司；通用人形机器人</t>
         </is>
       </c>
     </row>
@@ -1863,22 +1863,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>它石智航</t>
+          <t>智平方</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>上海它石智航技术有限公司</t>
+          <t>智平方(深圳)科技股份有限公司</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>上海市徐汇区桂平路391号2号楼21层</t>
+          <t>深圳市南山区桃源街道福光社区留仙大道3370号南山智园崇文园区1号楼1904</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1888,27 +1888,27 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>陈亦伦</t>
+          <t>郭彦东</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>91310120MADR48R94G</t>
+          <t>91440300MA5HTHDC7C</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>214.8745万元</t>
+          <t>249.3648万元</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Tashi Zhihang Technology Co., Ltd.；创始人陈亦伦为华为车BU前首席科学家；联创李震宇前百度自动驾驶负责人；百度/美团/高瓴/红杉投资</t>
+          <t>Zhifang (Shenzhen) Technology Co., Ltd.；郭彦东博士(前OPPO/小鹏AI首席科学家)创建；AlphaBot通用机器人；估值约200亿</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>加速进化</t>
+          <t>松延动力</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>北京加速进化科技有限公司</t>
+          <t>北京松延动力科技集团股份有限公司</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>北京市海淀区清河永泰庄村东16幢平房301</t>
+          <t>北京市昌平区未来科技城滨河大道3号院1号楼1601-1606房间</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1945,27 +1945,27 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>程昊</t>
+          <t>姜哲源</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>91110108MACN3TDP28</t>
+          <t>91110114MACYMUGC1P</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>415.7329万元</t>
+          <t>459.6054万元</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Beijing Accelerated Evolution Technology Co., Ltd.；清华火神足球队背景；Booster T1人形机器人</t>
+          <t>Songyan Power (Beijing) Technology Co., Ltd.；清华交叉信息学院背景；N2/S1人形机器人</t>
         </is>
       </c>
     </row>
@@ -1977,52 +1977,52 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>帕西尼</t>
+          <t>它石智航</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>帕西尼感知科技(深圳)有限公司</t>
+          <t>上海它石智航技术有限公司</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>深圳市南山区西丽街道西丽社区打石二路万科云城六期一栋云中城B805(一照多址)</t>
+          <t>上海市徐汇区桂平路391号2号楼21层</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>计算机/通信/电子设备制造业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>许晋诚</t>
+          <t>陈亦伦</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>91440300MA5GURGH9P</t>
+          <t>91310120MADR48R94G</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>1112.3032万元</t>
+          <t>214.8745万元</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Pasini Perception Technology (Shenzhen) Co., Ltd.；多维触觉传感「卖水人」；股东含比亚迪、京东、新奥、北汽安鹏</t>
+          <t>Shanghai Tashi Zhihang Technology Co., Ltd.；创始人陈亦伦为华为车BU前首席科学家；联创李震宇前百度自动驾驶负责人；百度/美团/高瓴/红杉投资</t>
         </is>
       </c>
     </row>
@@ -2034,52 +2034,52 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>魔法原子</t>
+          <t>加速进化</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>魔法原子机器人科技(无锡)有限公司</t>
+          <t>北京加速进化科技有限公司</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>无锡</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>无锡市梁溪区江海西路98号</t>
+          <t>北京市海淀区清河永泰庄村东16幢平房301</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>通用设备制造业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>陈春玉</t>
+          <t>程昊</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>91110400MAD7BLY00Q</t>
+          <t>91110108MACN3TDP28</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>10000万元</t>
+          <t>415.7329万元</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Magic Atomic Robotics Technology (Wuxi) Co., Ltd.；曾用名 魔法原子机器人科技(北京)有限公司；创始人吴长征(前小米机器人/普渡)；央视春晚机器人</t>
+          <t>Beijing Accelerated Evolution Technology Co., Ltd.；清华火神足球队背景；Booster T1人形机器人</t>
         </is>
       </c>
     </row>
@@ -2091,52 +2091,52 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>卓益得</t>
+          <t>帕西尼</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上海卓益得机器人有限公司</t>
+          <t>帕西尼感知科技(深圳)有限公司</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>上海市浦东新区周邓公路5318号4幢6层、7层</t>
+          <t>深圳市南山区西丽街道西丽社区打石二路万科云城六期一栋云中城B805(一照多址)</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>软件和信息服务业</t>
+          <t>计算机/通信/电子设备制造业</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>李清都</t>
+          <t>许晋诚</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>91310110MA1G9BR12D</t>
+          <t>91440300MA5GURGH9P</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>467.645万元</t>
+          <t>1112.3032万元</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Shanghai Zhuoyide Robotics Co., Ltd.；双足机器人；上海理工大学背景</t>
+          <t>Pasini Perception Technology (Shenzhen) Co., Ltd.；多维触觉传感「卖水人」；股东含比亚迪、京东、新奥、北汽安鹏</t>
         </is>
       </c>
     </row>
@@ -2148,52 +2148,52 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>灵宝CASBOT</t>
+          <t>魔法原子</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>北京中科慧灵机器人技术有限公司</t>
+          <t>魔法原子机器人科技(无锡)有限公司</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>无锡</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>北京市海淀区西小口路66号中关村东升科技园·北领地B-2楼1层B103室</t>
+          <t>无锡市梁溪区江海西路98号</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>专用设备制造业</t>
+          <t>通用设备制造业</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>杨平</t>
+          <t>陈春玉</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>91110108MACTD92T0K</t>
+          <t>91110400MAD7BLY00Q</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>148.6787万元</t>
+          <t>10000万元</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Beijing Zhongke Huiling Robot Technology Co., Ltd.；中科院自动化所张正涛创办；CASBOT具身人形机器人</t>
+          <t>Magic Atomic Robotics Technology (Wuxi) Co., Ltd.；曾用名 魔法原子机器人科技(北京)有限公司；创始人吴长征(前小米机器人/普渡)；央视春晚机器人</t>
         </is>
       </c>
     </row>
@@ -2205,52 +2205,52 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>大象机器人</t>
+          <t>卓益得</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>深圳市大象机器人科技有限公司</t>
+          <t>上海卓益得机器人有限公司</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>深圳市福田区华强北街道福强社区深南中路2070号中电广场大厦5层D5F05室</t>
+          <t>上海市浦东新区周邓公路5318号4幢6层、7层</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>通用设备制造业</t>
+          <t>软件和信息服务业</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>伍祁林</t>
+          <t>李清都</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>91440300MA5DJ0Y914</t>
+          <t>91310110MA1G9BR12D</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>2016-08-10</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>324.7832万元</t>
+          <t>467.645万元</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Shenzhen Elephant Robotics Technology Co., Ltd.；协作机械臂+人形/四足；教育消费级</t>
+          <t>Shanghai Zhuoyide Robotics Co., Ltd.；双足机器人；上海理工大学背景</t>
         </is>
       </c>
     </row>
@@ -2262,52 +2262,52 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>达闼</t>
+          <t>灵宝CASBOT</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>达闼机器人股份有限公司</t>
+          <t>北京中科慧灵机器人技术有限公司</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>上海市闵行区东川路3966号3幢1层</t>
+          <t>北京市海淀区西小口路66号中关村东升科技园·北领地B-2楼1层B103室</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>科技推广和应用服务业</t>
+          <t>专用设备制造业</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>HUANG WILLIAM XIAO-QING(黄晓庆)</t>
+          <t>杨平</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>91310112MA1GC78A07</t>
+          <t>91110108MACTD92T0K</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>138742.1338万元</t>
+          <t>148.6787万元</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Dataa Robotics Co., Ltd.；曾用名 达闼机器人有限公司；云端智能机器人；估值曾超200亿</t>
+          <t>Beijing Zhongke Huiling Robot Technology Co., Ltd.；中科院自动化所张正涛创办；CASBOT具身人形机器人</t>
         </is>
       </c>
     </row>
@@ -2319,52 +2319,52 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>维他动力</t>
+          <t>大象机器人</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>维他动力(北京)科技有限公司</t>
+          <t>深圳市大象机器人科技有限公司</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>北京市海淀区宝盛南路1号院20号楼3层101</t>
+          <t>深圳市福田区华强北街道福强社区深南中路2070号中电广场大厦5层D5F05室</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>科技推广和应用服务业</t>
+          <t>通用设备制造业</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>余轶南</t>
+          <t>伍祁林</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>91110108MAE7TDFY61</t>
+          <t>91440300MA5DJ0Y914</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2016-08-10</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>176.4449万元</t>
+          <t>324.7832万元</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Vita Power (Beijing) Technology Co., Ltd.；创始人余轶南前地平线副总裁；消费级具身智能</t>
+          <t>Shenzhen Elephant Robotics Technology Co., Ltd.；协作机械臂+人形/四足；教育消费级</t>
         </is>
       </c>
     </row>
@@ -2376,52 +2376,52 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>越疆科技</t>
+          <t>达闼</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>深圳市越疆科技股份有限公司</t>
+          <t>达闼机器人股份有限公司</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>深圳市南山区桃源街道福光社区留仙大道3370号南山智园崇文园区2号楼1003</t>
+          <t>上海市闵行区东川路3966号3幢1层</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>计算机/通信/电子设备制造业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>刘培超</t>
+          <t>HUANG WILLIAM XIAO-QING(黄晓庆)</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>91440300349770526R</t>
+          <t>91310112MA1GC78A07</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>2015-07-30</t>
+          <t>2018-10-17</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>43995.54万元</t>
+          <t>138742.1338万元</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Dobot；港股02432.HK；协作机器人+人形机器人Dobot Atom；国家制造业基金/深创投等持股</t>
+          <t>Dataa Robotics Co., Ltd.；曾用名 达闼机器人有限公司；云端智能机器人；估值曾超200亿</t>
         </is>
       </c>
     </row>
@@ -2433,22 +2433,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>优艾智合</t>
+          <t>维他动力</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>深圳优艾智合机器人科技有限公司</t>
+          <t>维他动力(北京)科技有限公司</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>深圳市龙岗区吉华街道甘坑社区甘李二路9号金苹果创新园厂房C101</t>
+          <t>北京市海淀区宝盛南路1号院20号楼3层101</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -2458,27 +2458,27 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>张朝辉</t>
+          <t>余轶南</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>91440300MA5F0TBK2B</t>
+          <t>91110108MAE7TDFY61</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>2018-03-05</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>10000万元</t>
+          <t>176.4449万元</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>YouiBot；半导体/能源化工移动操作机器人；专精特新小巨人</t>
+          <t>Vita Power (Beijing) Technology Co., Ltd.；创始人余轶南前地平线副总裁；消费级具身智能</t>
         </is>
       </c>
     </row>
@@ -2490,52 +2490,52 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>珞石机器人</t>
+          <t>越疆科技</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>珞石(山东)机器人集团股份有限公司（曾用名 珞石(北京)科技有限公司）</t>
+          <t>深圳市越疆科技股份有限公司</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>济宁</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>山东省济宁市邹城市中心店镇中心机电产业园华润路888号</t>
+          <t>深圳市南山区桃源街道福光社区留仙大道3370号南山智园崇文园区2号楼1003</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>科技推广和应用服务业</t>
+          <t>计算机/通信/电子设备制造业</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>庹华</t>
+          <t>刘培超</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>9111010831831195XM</t>
+          <t>91440300349770526R</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>2014-12-15</t>
+          <t>2015-07-30</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>2386.9429万元</t>
+          <t>43995.54万元</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Rokae；协作机器人+人形机器人；北京/上海/深圳设研发中心；港股03752拟上市，估值约53亿；国家制造业转型升级基金持股</t>
+          <t>Dobot；港股02432.HK；协作机器人+人形机器人Dobot Atom；国家制造业基金/深创投等持股</t>
         </is>
       </c>
     </row>
@@ -2547,22 +2547,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>节卡机器人</t>
+          <t>优艾智合</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>节卡机器人股份有限公司</t>
+          <t>深圳优艾智合机器人科技有限公司</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>上海市闵行区剑川路646号6幢</t>
+          <t>深圳市龙岗区吉华街道甘坑社区甘李二路9号金苹果创新园厂房C101</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -2572,27 +2572,27 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>李明洋</t>
+          <t>张朝辉</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>9131000039865525XN</t>
+          <t>91440300MA5F0TBK2B</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>2014-07-15</t>
+          <t>2018-03-05</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>6364.0765万元</t>
+          <t>10000万元</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>JAKA；协作机器人国内销量第一(2024)；科创板受理；牵头制定机器人视觉国标</t>
+          <t>YouiBot；半导体/能源化工移动操作机器人；专精特新小巨人</t>
         </is>
       </c>
     </row>
@@ -2604,22 +2604,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>遨博智能</t>
+          <t>珞石机器人</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>遨博(北京)智能科技股份有限公司（曾用名 遨博(北京)智能科技有限公司）</t>
+          <t>珞石(山东)机器人集团股份有限公司（曾用名 珞石(北京)科技有限公司）</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>济宁</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>北京市门头沟区莲石湖西路98号院5号楼407室</t>
+          <t>山东省济宁市邹城市中心店镇中心机电产业园华润路888号</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -2629,27 +2629,27 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>魏洪兴</t>
+          <t>庹华</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>91110109330285061E</t>
+          <t>9111010831831195XM</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>2015-01-21</t>
+          <t>2014-12-15</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>10307.8618万元</t>
+          <t>2386.9429万元</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>AUBO；协作机器人国家标准制定者；国产协作机器人龙头</t>
+          <t>Rokae；协作机器人+人形机器人；北京/上海/深圳设研发中心；港股03752拟上市，估值约53亿；国家制造业转型升级基金持股</t>
         </is>
       </c>
     </row>
@@ -2661,52 +2661,52 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>大族机器人</t>
+          <t>节卡机器人</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>深圳市大族机器人有限公司</t>
+          <t>节卡机器人股份有限公司</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>深圳市宝安区福海街道和平社区重庆路12号智造中心园3栋厂房601</t>
+          <t>上海市闵行区剑川路646号6幢</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>软件和信息技术服务业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>王光能</t>
+          <t>李明洋</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>91440300MA5EQ6JAX4</t>
+          <t>9131000039865525XN</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2014-07-15</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>8180万元</t>
+          <t>6364.0765万元</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Hans Robot；大族激光(002008)控股子公司；协作+移动操作机器人；B+轮</t>
+          <t>JAKA；协作机器人国内销量第一(2024)；科创板受理；牵头制定机器人视觉国标</t>
         </is>
       </c>
     </row>
@@ -2718,22 +2718,22 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>非夕科技</t>
+          <t>遨博智能</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>上海非夕机器人科技有限公司</t>
+          <t>遨博(北京)智能科技股份有限公司（曾用名 遨博(北京)智能科技有限公司）</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>上海市闵行区东川路555号丙楼1096室</t>
+          <t>北京市门头沟区莲石湖西路98号院5号楼407室</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -2743,27 +2743,27 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>王世全</t>
+          <t>魏洪兴</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>91310112MA1GBEPY9P</t>
+          <t>91110109330285061E</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>2016-11-17</t>
+          <t>2015-01-21</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>30000万元</t>
+          <t>10307.8618万元</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Flexiv；自适应机器人(力控+AI)；斯坦福团队；C+轮估值65亿；国家级独角兽</t>
+          <t>AUBO；协作机器人国家标准制定者；国产协作机器人龙头</t>
         </is>
       </c>
     </row>
@@ -2775,52 +2775,52 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>梅卡曼德</t>
+          <t>大族机器人</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>梅卡曼德(北京)机器人科技有限公司（现 梅卡曼德(雄安)机器人科技股份有限公司）</t>
+          <t>深圳市大族机器人有限公司</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>北京市海淀区上地信息产业基地创业路6号1层1100</t>
+          <t>深圳市宝安区福海街道和平社区重庆路12号智造中心园3栋厂房601</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>科技推广和应用服务业</t>
+          <t>软件和信息技术服务业</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>邵天兰</t>
+          <t>王光能</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>91110108MA0086HR6G</t>
+          <t>91440300MA5EQ6JAX4</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>2016-09-12</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>509.3523万元</t>
+          <t>8180万元</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Mech-Mind；AI+3D视觉+工业机器人；美团/红杉/英特尔投资；国家级专精特新小巨人</t>
+          <t>Hans Robot；大族激光(002008)控股子公司；协作+移动操作机器人；B+轮</t>
         </is>
       </c>
     </row>
@@ -2832,22 +2832,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>普渡科技</t>
+          <t>非夕科技</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>深圳市普渡科技股份有限公司（曾用名 深圳市普渡科技有限公司）</t>
+          <t>上海非夕机器人科技有限公司</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道南坑社区雅星路8号星河WORLD双子塔.西塔6605-4</t>
+          <t>上海市闵行区东川路555号丙楼1096室</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2857,27 +2857,27 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>张涛</t>
+          <t>王世全</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>91440300359857967F</t>
+          <t>91310112MA1GBEPY9P</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>2016-01-13</t>
+          <t>2016-11-17</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>21138.4615万元</t>
+          <t>30000万元</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>Pudu；商用配送/清洁机器人；全球60+国家；E轮；美团战略投资</t>
+          <t>Flexiv；自适应机器人(力控+AI)；斯坦福团队；C+轮估值65亿；国家级独角兽</t>
         </is>
       </c>
     </row>
@@ -2889,52 +2889,52 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>高仙机器人</t>
+          <t>梅卡曼德</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>上海高仙自动化科技发展股份有限公司（曾用名 上海高仙自动化科技发展有限公司）</t>
+          <t>梅卡曼德(北京)机器人科技有限公司（现 梅卡曼德(雄安)机器人科技股份有限公司）</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>上海市徐汇区嘉川路245号2号楼204室</t>
+          <t>北京市海淀区上地信息产业基地创业路6号1层1100</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>软件和信息技术服务业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>程昊天</t>
+          <t>邵天兰</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>91310115080028627C</t>
+          <t>91110108MA0086HR6G</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>2013-10-10</t>
+          <t>2016-09-12</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>4025.4546万元</t>
+          <t>509.3523万元</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>GS Robotics；商用清洁机器人；全球40+国家、4亿公里清洁里程；D+轮</t>
+          <t>Mech-Mind；AI+3D视觉+工业机器人；美团/红杉/英特尔投资；国家级专精特新小巨人</t>
         </is>
       </c>
     </row>
@@ -2946,52 +2946,52 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>仙工智能</t>
+          <t>普渡科技</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>上海仙工智能科技股份有限公司（曾用名 上海仙工智能科技有限公司）</t>
+          <t>深圳市普渡科技股份有限公司（曾用名 深圳市普渡科技有限公司）</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>中国(上海)自由贸易试验区锦绣东路2777弄11号全幢</t>
+          <t>深圳市龙岗区坂田街道南坑社区雅星路8号星河WORLD双子塔.西塔6605-4</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>软件和信息技术服务业</t>
+          <t>科技推广和应用服务业</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>张涛</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>91310115MA1K4HX99N</t>
+          <t>91440300359857967F</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>2020-04-22</t>
+          <t>2016-01-13</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>10000万元</t>
+          <t>21138.4615万元</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>SEER；智能机器人控制器市占率第一+AMR+具身智能；IDG/科沃斯/华创投资；港股06106拟</t>
+          <t>Pudu；商用配送/清洁机器人；全球60+国家；E轮；美团战略投资</t>
         </is>
       </c>
     </row>
@@ -3003,52 +3003,52 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>灵动科技</t>
+          <t>高仙机器人</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>灵动科技(北京)有限公司（现 灵动科技(安徽)有限公司）</t>
+          <t>上海高仙自动化科技发展股份有限公司（曾用名 上海高仙自动化科技发展有限公司）</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>北京市海淀区清河新都东站南北京液压铸造厂36幢平房098号</t>
+          <t>上海市徐汇区嘉川路245号2号楼204室</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>科技推广和应用服务业</t>
+          <t>软件和信息技术服务业</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>齐欧</t>
+          <t>程昊天</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>91110108MA0053WG7U</t>
+          <t>91310115080028627C</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2013-10-10</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>3150万元</t>
+          <t>4025.4546万元</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>ForwardX；视觉AMR自主移动机器人；C轮；钟鼎/鼎晖投资；注册地已迁合肥</t>
+          <t>GS Robotics；商用清洁机器人；全球40+国家、4亿公里清洁里程；D+轮</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>星猿哲</t>
+          <t>仙工智能</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>星猿哲科技(上海)有限公司</t>
+          <t>上海仙工智能科技股份有限公司（曾用名 上海仙工智能科技有限公司）</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3075,37 +3075,37 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>上海市闵行区银都路4277号7幢</t>
+          <t>中国(上海)自由贸易试验区锦绣东路2777弄11号全幢</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>通用设备制造业</t>
+          <t>软件和信息技术服务业</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>周佳骥</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>91310000MA1GC2QU5D</t>
+          <t>91310115MA1K4HX99N</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2020-04-22</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>10000万美元</t>
+          <t>10000万元</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>XYZ Robotics；3D视觉+抓取自动化分拣/拆码垛；B+轮；CMU/MIT团队</t>
+          <t>SEER；智能机器人控制器市占率第一+AMR+具身智能；IDG/科沃斯/华创投资；港股06106拟</t>
         </is>
       </c>
     </row>
@@ -3117,228 +3117,1311 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>灵动科技</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>灵动科技(北京)有限公司（现 灵动科技(安徽)有限公司）</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>北京市海淀区清河新都东站南北京液压铸造厂36幢平房098号</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>齐欧</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>91110108MA0053WG7U</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>3150万元</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>ForwardX；视觉AMR自主移动机器人；C轮；钟鼎/鼎晖投资；注册地已迁合肥</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>星猿哲</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>星猿哲科技(上海)有限公司</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>上海市闵行区银都路4277号7幢</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>通用设备制造业</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>周佳骥</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>91310000MA1GC2QU5D</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>2018-06-27</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>10000万美元</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>XYZ Robotics；3D视觉+抓取自动化分拣/拆码垛；B+轮；CMU/MIT团队</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>可以科技</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>北京可以科技有限公司</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>北京市海淀区中关村南大街5号9区685栋5层01室</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>计算机/通信/电子设备制造业</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>杨健勃</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>911101080573032055</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>2014-03-18</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>100.874万元</t>
         </is>
       </c>
-      <c r="K47" s="6" t="inlineStr">
+      <c r="K49" s="6" t="inlineStr">
         <is>
           <t>Keyi/ClicBot/Loona；消费级模块化+陪伴机器人；D轮；小米/顺为投资</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>北京人形机器人创新中心</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>北京人形机器人创新中心有限公司</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>北京市北京经济技术开发区经海五路3号院46号楼1层101</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>熊友军</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>91110400MAD3Q0NU7N</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>60122.77万元</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>国家级人形机器人创新平台；股东含小米、优必选、京城机电等</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>理工华汇</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>北京理工华汇智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>北京市海淀区中关村南大街甲12号1幢四层412</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>张伟民</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>911101083579322497</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>1833.26万元</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>北理工人形机器人学科性公司；创始人黄强(仿人机器人专家)；足式/人形本体</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>破壳机器人</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>破壳（北京）智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>北京市海淀区中关村大街32号5层A0485</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>赵佳馨</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>91110108MAK89M552R</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>750万元</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>家庭服务机器人(轮式底盘+双臂)；创始人许华哲(星海图前首席科学家、清华交叉信息研究院)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>方石机器人</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>北京方石机器人有限公司</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>北京市北京经济技术开发区科创三街18号院1号楼6层6A-16</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>研究和试验发展</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>李思桥</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>91330402MA2CX6EW98</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>565.0685万元</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>曾用名 嘉兴方石科技有限公司；工业/商业清洁与服务机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>月泉仿生</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>北京达奇月泉仿生科技有限公司</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>北京市昌平区未来科学城</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>李天灵</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>91110114MAC27YU611</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>864.40万元</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>博文W-Bot轮式人形整机、Y-Hand仿生灵巧手；中科院任露泉院士领衔；仿生拉压体机器人理论</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>猎户星空</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>北京猎户星空科技有限公司</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>北京市石景山区和平西路60号院</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>刘媛媛</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>91110107MA008AYB44</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>2016-09-19</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>3568.06万元</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>OrionStar；豹小秘/豹小递系列服务机器人；猎豹移动(傅盛)系；AI+软件+硬件+服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>思灵机器人</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>北京思灵机器人科技有限责任公司</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>北京市海淀区永泰庄北路</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>陈兆芃</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>91110108MA01DMU77F</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>2018-07-24</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2000万元</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>Agile Robots；DIANA智能力控机械臂、仿人五指灵巧手；德国航空航天中心(DLR)孵化</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>动易科技</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>广州动易人工智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>广州市海珠区大干围路38号第五工业区11号楼106室</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>研究和试验发展</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>任晓雨</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>91440105MAEK5JDY0Q</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>5503万元</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>PHYBOT；M1通用人形/C1伙伴型机器人；强化学习用于全尺寸人形运动控制；获超亿元融资</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>千诀科技</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>北京千诀科技有限公司</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>北京市朝阳区速滑馆南路甲1号院1号楼-2至3层101内1层F1-14</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>软件和信息技术服务业</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>高海川</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>91110108MACMEFMP0J</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>212.8311万元</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>PolibrainOS(千诀大脑)；类脑机器人大脑；清华类脑计算研究中心孵化；接入终端达十万台量级</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>元节智能</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>北京元节智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>北京市海淀区中关村大街18号</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>王栋</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>91110108MAKA9RH621</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>500万元</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>AtomBite.AI；外卖打包机器人M1/油炸工作站M2/后厨指挥M3；前美团外卖CTO王栋(清华)创立；RaaS模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>清研精准</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>清研精准(北京)汽车科技有限公司</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>北京市北京经济技术开发区荣华南路13号院7号楼3层307</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>董汉</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>91110302MA01HBAX4N</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>2019-02-22</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>5000万元</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>物理AI工程化底座；TsingLoop多模态数据管线、Robot-in-the-Loop测试体系；具身Infra卖铲人；B轮数亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>诺亦腾</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>诺亦腾机器人科技(北京)有限公司</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>北京市海淀区小月河东畔路16号院2号楼6层601-604号</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>其他技术推广服务</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>戴若犂</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>91110108MAEEKYRGX9</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>158.3165万元</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>Noitom Robotics；动作捕捉数据采集；母集团北京诺亦腾科技(2012)为动作捕捉龙头</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>阿米奥机器人</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>北京阿米奥机器人科技有限公司</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>北京市石景山区料仓路6号院15号楼3层101E室</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>刘方</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>91110107MAE1BR4E7R</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>14.836232万元</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>Amio；原小米汽车自动驾驶负责人刘方创立；专注规模化商业场景机器人应用；天使轮亿级</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>零次方机器人</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>合肥零次方机器人有限公司</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>安徽省合肥市包河区中国视界</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>闵宇恒</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>91340111MAE92K2J4F</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>141.94万元</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>清华与江淮前沿技术协同创新中心联合孵化；具身智能本体研发</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>光象科技</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>光象（北京）科技有限公司</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>北京市海淀区中关村东路1号院9号楼</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>张涛</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>91110108MAEJ27J94D</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>1004.32万元</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>清华车辆与运载学院/人工智能学院科技成果转化；物理原生具身智能；种子轮数千万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>极智嘉</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>北京极智嘉科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>雄安</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>河北省雄安新区人工智能产业园</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>郑勇</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>91110117330386452K</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>2015-02-03</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>133728.70万元</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>Geek+；AMR仓储物流机器人龙头；港股02590.HK；全球AMR市占率领先</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>⚪ 公海</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>新石器</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>新石器慧通（北京）科技有限公司</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>北京市北京经济技术开发区荣华中路10号院</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>科技推广和应用服务业</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>李子夷</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>91110105MA01AEWR5C</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>2018-02-13</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>5016.85万元</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>Neolix；L4级无人车/物流配送车独角兽；校园/园区/封闭场景运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>🔴 竞品锁定</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>智元机器人</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>智元创新(上海)科技股份有限公司</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>上海市浦东新区秀浦路2555号29幢8层</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>专业技术服务业</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>邓泰华</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>91310000MACA4F0G12</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>2023-02-27</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>9195.87万元</t>
         </is>
       </c>
-      <c r="K48" s="6" t="inlineStr">
+      <c r="K67" s="6" t="inlineStr">
         <is>
           <t>AGIBOT；华为/腾讯生态强绑定</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>🔴 竞品锁定</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>优必选</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>深圳市优必选科技股份有限公司</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>深圳市南山区桃源街道长源社区学苑大道1001号南山智园C1栋2201</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <t>专业技术服务业</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>周剑</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>91440300593047655L</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>2012-03-31</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>50340.14万元</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
+      <c r="K68" s="6" t="inlineStr">
         <is>
           <t>港股 09880.HK；腾讯参投</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>🔴 竞品锁定</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>云迹科技</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>北京云迹科技股份有限公司</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>北京市北京经济技术开发区(通州)经海五路3号院5号楼1层102室</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>计算机/通信/电子设备制造业</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>胡泉（董事长 支涛）</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>911101080918690509</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
         <is>
           <t>2014-01-29</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>6181.8182万元</t>
         </is>
       </c>
-      <c r="K50" s="6" t="inlineStr">
+      <c r="K69" s="6" t="inlineStr">
         <is>
           <t>Yunji；酒店/服务机器人(具身服务智能体)；港股2670.HK；腾讯(林芝腾讯)持股，归入腾讯生态</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K50"/>
+  <autoFilter ref="A2:K69"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -3375,7 +4458,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>共 48 家（🟢 无影客户:1家；🔵 关联可争取:7家；⚪ 公海:37家；🔴 竞品锁定:3家）；覆盖全国主要具身智能企业（人形机器人/具身大模型/仿真数据/触觉传感）</t>
+          <t>共 67 家（🟢 无影客户:1家；🔵 关联可争取:9家；⚪ 公海:54家；🔴 竞品锁定:3家）；覆盖全国主要具身智能企业（人形机器人/具身大模型/仿真数据/触觉传感）</t>
         </is>
       </c>
     </row>
